--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광명시 하안로288번길 15 조일프라자 5층</t>
+          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43k9f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1601</v>
+        <v>1609</v>
       </c>
       <c r="Q2" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="R2" t="n">
-        <v>1939</v>
+        <v>1951</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인스타짐 광명역점</t>
+          <t>클리어짐 철산역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>instargymgm@naver.com</t>
+          <t>cleargym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1436-8069</t>
+          <t>0507-1371-1045</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instargym_gm/</t>
+          <t>https://blog.naver.com/cleargym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/witsh32</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>890</v>
+        <v>1907</v>
       </c>
       <c r="Q3" t="n">
-        <v>354</v>
+        <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>1244</v>
+        <v>2531</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1471490398</t>
+          <t>1477285733</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471490398</t>
+          <t>https://m.place.naver.com/place/1477285733</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>클리어짐 철산역점</t>
+          <t>바디채널&amp;바레톤 광명사거리역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cleargym@naver.com</t>
+          <t>bodychannelg@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1371-1045</t>
+          <t>0507-1419-4015</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기도 광명시 오리로 992 12층 1201호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym</t>
+          <t>https://blog.naver.com/bodychannelg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcsoke</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1886</v>
+        <v>442</v>
       </c>
       <c r="Q4" t="n">
-        <v>620</v>
+        <v>1671</v>
       </c>
       <c r="R4" t="n">
-        <v>2506</v>
+        <v>2113</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1477285733</t>
+          <t>1349719442</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477285733</t>
+          <t>https://m.place.naver.com/place/1349719442</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 865 601호</t>
+          <t>경기도 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4y72y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>638</v>
+        <v>662</v>
       </c>
       <c r="Q5" t="n">
         <v>445</v>
       </c>
       <c r="R5" t="n">
-        <v>1083</v>
+        <v>1107</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c1ao</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="Q6" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="R6" t="n">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디채널&amp;바레톤 광명사거리역점</t>
+          <t>하데스클럽 광명하안점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodychannelg@naver.com</t>
+          <t>tina09now@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1419-4015</t>
+          <t>0507-1307-7359</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 992 12층 1201호</t>
+          <t>경기도 광명시 범안로 1055 10층 전관</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannelg</t>
+          <t>https://www.instagram.com/SAN__KYU/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4k4y2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>439</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>1653</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>2092</v>
+        <v>47</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,56 +1106,60 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1349719442</t>
+          <t>2091152989</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349719442</t>
+          <t>https://m.place.naver.com/place/2091152989</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하데스클럽 광명하안점</t>
+          <t>휘트니스피플 우먼 철산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yyolooo@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1307-7359</t>
+          <t>02-2625-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 광명시 범안로 1055 10층 전관</t>
+          <t>경기도 광명시 오리로856번길 11 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/SAN__KYU/</t>
+          <t>https://fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,22 +1169,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wac1b45</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>462</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>485</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>947</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2091152989</t>
+          <t>1239968125</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091152989</t>
+          <t>https://m.place.naver.com/place/1239968125</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,38 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 철산점</t>
+          <t>원앤온리짐 광명철산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
+          <t>one_and_only_gym_cs@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-2625-3912</t>
+          <t>0507-1465-8312</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 11 5층</t>
+          <t>경기도 광명시 디지털로 17 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://fitnesspeople.co.kr/</t>
+          <t>https://blog.naver.com/one_and_only_gym_cs</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1296,32 +1268,28 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgyxanj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>455</v>
+        <v>227</v>
       </c>
       <c r="Q9" t="n">
-        <v>483</v>
+        <v>197</v>
       </c>
       <c r="R9" t="n">
-        <v>938</v>
+        <v>424</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1239968125</t>
+          <t>1499783974</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239968125</t>
+          <t>https://m.place.naver.com/place/1499783974</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1320,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>원앤온리짐 광명철산점</t>
+          <t>엔짐 철산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>one_and_only_gym_cs@naver.com</t>
+          <t>ngym_cs@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1465-8312</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 광명시 디지털로 17 3층</t>
+          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/one_and_only_gym_cs</t>
+          <t>https://blog.naver.com/ngym_cs</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1394,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41agt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>226</v>
+        <v>145</v>
       </c>
       <c r="Q10" t="n">
-        <v>199</v>
+        <v>46</v>
       </c>
       <c r="R10" t="n">
-        <v>425</v>
+        <v>191</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,47 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1499783974</t>
+          <t>2058915002</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1499783974</t>
+          <t>https://m.place.naver.com/place/2058915002</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>필라테스린 광명점</t>
+          <t>바디채움PT&amp;운동센터 하안점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilateslean_gm@naver.com</t>
+          <t>bodychaeum@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1378-6854</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 346 4층 401호</t>
+          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_gm</t>
+          <t>https://blog.naver.com/bodychaeum</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1488,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sq60</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1507,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="Q11" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="R11" t="n">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1139300027</t>
+          <t>1473047975</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139300027</t>
+          <t>https://m.place.naver.com/place/1473047975</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스엠 헬스&amp;pt 하안점</t>
+          <t>인스타짐 광명역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessm10@naver.com</t>
+          <t>instargymgm@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1444-0167</t>
+          <t>0507-1436-8069</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
+          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AZJAG</t>
+          <t>https://www.instagram.com/instargym_gm/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/witsh32</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1609</v>
+        <v>894</v>
       </c>
       <c r="Q2" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="R2" t="n">
-        <v>1951</v>
+        <v>1255</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20076918</t>
+          <t>1471490398</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20076918</t>
+          <t>https://m.place.naver.com/place/1471490398</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcsoke</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1907</v>
+        <v>1918</v>
       </c>
       <c r="Q3" t="n">
         <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>2531</v>
+        <v>2542</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로 992 12층 1201호</t>
+          <t>경기 광명시 오리로 992 12층 1201호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k4y2</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +824,10 @@
         <v>442</v>
       </c>
       <c r="Q4" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="R4" t="n">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로 865 601호</t>
+          <t>경기 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4y72y</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Q5" t="n">
         <v>445</v>
       </c>
       <c r="R5" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c1ao</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1020,10 @@
         <v>573</v>
       </c>
       <c r="Q6" t="n">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="R6" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하데스클럽 광명하안점</t>
+          <t>클리어짐 광명역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tina09now@naver.com</t>
+          <t>cleargym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1307-7359</t>
+          <t>0507-1342-0538</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 광명시 범안로 1055 10층 전관</t>
+          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/SAN__KYU/</t>
+          <t>https://blog.naver.com/cleargym2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48j21</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>17</v>
+        <v>961</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="R7" t="n">
-        <v>47</v>
+        <v>1208</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2091152989</t>
+          <t>1099783664</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091152989</t>
+          <t>https://m.place.naver.com/place/1099783664</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1173,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로856번길 11 5층</t>
+          <t>경기 광명시 오리로856번길 11 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,10 +1198,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgyxanj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1189,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Q8" t="n">
         <v>485</v>
       </c>
       <c r="R8" t="n">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1214,7 +1242,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1254,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>원앤온리짐 광명철산점</t>
+          <t>엔짐 철산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>one_and_only_gym_cs@naver.com</t>
+          <t>ngym_cs@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1465-8312</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 광명시 디지털로 17 3층</t>
+          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/one_and_only_gym_cs</t>
+          <t>https://blog.naver.com/ngym_cs</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzcy70h</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="Q9" t="n">
-        <v>197</v>
+        <v>46</v>
       </c>
       <c r="R9" t="n">
-        <v>424</v>
+        <v>190</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,47 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1499783974</t>
+          <t>2058915002</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1499783974</t>
+          <t>https://m.place.naver.com/place/2058915002</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔짐 철산점</t>
+          <t>바디채움PT&amp;운동센터 하안점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ngym_cs@naver.com</t>
+          <t>bodychaeum@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1378-6854</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ngym_cs</t>
+          <t>https://blog.naver.com/bodychaeum</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wlkbwl8</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="R10" t="n">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2058915002</t>
+          <t>1473047975</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058915002</t>
+          <t>https://m.place.naver.com/place/1473047975</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디채움PT&amp;운동센터 하안점</t>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodychaeum@naver.com</t>
+          <t>gym101@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1378-6854</t>
+          <t>0507-1330-3078</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+          <t>경기 광명시 광명로 841 B1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychaeum</t>
+          <t>https://www.instagram.com/gym101_gwangmyeong</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1483,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxgpr6n</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62</v>
+        <v>407</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="R11" t="n">
-        <v>229</v>
+        <v>666</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1522,115 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1473047975</t>
+          <t>1261214988</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473047975</t>
+          <t>https://m.place.naver.com/place/1261214988</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>앤티크짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>antiquegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1357-0064</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 광명시 양지로 19 유플래닛 어반브릭스 B동 433호 429호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/antiquegym</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40e5k</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>388</v>
+      </c>
+      <c r="R12" t="n">
+        <v>731</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1638569769</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1638569769</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>인스타짐 광명역점</t>
+          <t>휘트니스엠 헬스&amp;pt 하안점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>instargymgm@naver.com</t>
+          <t>fitnessm10@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-8069</t>
+          <t>0507-1444-0167</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기 광명시 하안로288번길 15 조일프라자 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instargym_gm/</t>
+          <t>http://pf.kakao.com/_AZJAG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/witsh32</t>
+          <t>https://talk.naver.com/ct/w43k9f</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>894</v>
+        <v>1612</v>
       </c>
       <c r="Q2" t="n">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="R2" t="n">
-        <v>1255</v>
+        <v>1954</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1471490398</t>
+          <t>20076918</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471490398</t>
+          <t>https://m.place.naver.com/place/20076918</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>클리어짐 철산역점</t>
+          <t>인스타짐 광명역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cleargym@naver.com</t>
+          <t>instargymgm@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1371-1045</t>
+          <t>0507-1436-8069</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym</t>
+          <t>https://www.instagram.com/instargym_gm/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsoke</t>
+          <t>https://talk.naver.com/ct/witsh32</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1918</v>
+        <v>894</v>
       </c>
       <c r="Q3" t="n">
-        <v>624</v>
+        <v>361</v>
       </c>
       <c r="R3" t="n">
-        <v>2542</v>
+        <v>1255</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1477285733</t>
+          <t>1471490398</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477285733</t>
+          <t>https://m.place.naver.com/place/1471490398</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디채널&amp;바레톤 광명사거리역점</t>
+          <t>클리어짐 철산역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bodychannelg@naver.com</t>
+          <t>cleargym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1419-4015</t>
+          <t>0507-1371-1045</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 992 12층 1201호</t>
+          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannelg</t>
+          <t>https://blog.naver.com/cleargym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4k4y2</t>
+          <t>https://talk.naver.com/ct/wcsoke</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>442</v>
+        <v>1918</v>
       </c>
       <c r="Q4" t="n">
-        <v>1672</v>
+        <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>2114</v>
+        <v>2542</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1349719442</t>
+          <t>1477285733</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349719442</t>
+          <t>https://m.place.naver.com/place/1477285733</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 철산점</t>
+          <t>바디채널&amp;바레톤 광명사거리역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboycs@naver.com</t>
+          <t>bodychannelg@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1427-8902</t>
+          <t>0507-1419-4015</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 865 601호</t>
+          <t>경기 광명시 오리로 992 12층 1201호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboycs/223877855300</t>
+          <t>https://blog.naver.com/bodychannelg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4y72y</t>
+          <t>https://talk.naver.com/ct/w4k4y2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>663</v>
+        <v>442</v>
       </c>
       <c r="Q5" t="n">
-        <v>445</v>
+        <v>1672</v>
       </c>
       <c r="R5" t="n">
-        <v>1108</v>
+        <v>2114</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1197140079</t>
+          <t>1349719442</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197140079</t>
+          <t>https://m.place.naver.com/place/1349719442</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>무브데이 PT 광명철산점</t>
+          <t>헬스보이짐 철산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>moveday01@naver.com</t>
+          <t>healthboycs@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1349-1693</t>
+          <t>0507-1427-8902</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/moveday01/223721875157</t>
+          <t>https://blog.naver.com/healthboycs/223877855300</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c1ao</t>
+          <t>https://talk.naver.com/ct/w4y72y</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>573</v>
+        <v>663</v>
       </c>
       <c r="Q6" t="n">
-        <v>748</v>
+        <v>445</v>
       </c>
       <c r="R6" t="n">
-        <v>1321</v>
+        <v>1108</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1505993596</t>
+          <t>1197140079</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505993596</t>
+          <t>https://m.place.naver.com/place/1197140079</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>클리어짐 광명역점</t>
+          <t>무브데이 PT 광명철산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cleargym2@naver.com</t>
+          <t>moveday01@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1342-0538</t>
+          <t>0507-1349-1693</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
+          <t>경기 광명시 오리로856번길 23 명산��딩 302호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym2</t>
+          <t>https://blog.naver.com/moveday01/223721875157</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48j21</t>
+          <t>https://talk.naver.com/ct/w4c1ao</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>961</v>
+        <v>572</v>
       </c>
       <c r="Q7" t="n">
-        <v>247</v>
+        <v>748</v>
       </c>
       <c r="R7" t="n">
-        <v>1208</v>
+        <v>1320</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1099783664</t>
+          <t>1505993596</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099783664</t>
+          <t>https://m.place.naver.com/place/1505993596</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,43 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 철산점</t>
+          <t>클리어짐 광명역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
+          <t>cleargym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-2625-3912</t>
+          <t>0507-1342-0538</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 11 5층</t>
+          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://fitnesspeople.co.kr/</t>
+          <t>https://blog.naver.com/cleargym2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1203,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgyxanj</t>
+          <t>https://talk.naver.com/ct/w48j21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>464</v>
+        <v>961</v>
       </c>
       <c r="Q8" t="n">
-        <v>485</v>
+        <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>949</v>
+        <v>1208</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1239968125</t>
+          <t>1099783664</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239968125</t>
+          <t>https://m.place.naver.com/place/1099783664</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1254,30 +1250,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔짐 철산점</t>
+          <t>휘트니스피플 우먼 철산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ngym_cs@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>02-2625-3912</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기 광명시 오리로856번길 11 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ngym_cs</t>
+          <t>https://fitnesspeople.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1297,12 +1301,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzcy70h</t>
+          <t>https://talk.naver.com/ct/wgyxanj</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>144</v>
+        <v>464</v>
       </c>
       <c r="Q9" t="n">
-        <v>46</v>
+        <v>485</v>
       </c>
       <c r="R9" t="n">
-        <v>190</v>
+        <v>949</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2058915002</t>
+          <t>1239968125</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058915002</t>
+          <t>https://m.place.naver.com/place/1239968125</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1347,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디채움PT&amp;운동센터 하안점</t>
+          <t>엔짐 철산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodychaeum@naver.com</t>
+          <t>ngym_cs@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1378-6854</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychaeum</t>
+          <t>https://blog.naver.com/ngym_cs</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlkbwl8</t>
+          <t>https://talk.naver.com/ct/wzcy70h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="Q10" t="n">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="R10" t="n">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1473047975</t>
+          <t>2058915002</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473047975</t>
+          <t>https://m.place.naver.com/place/2058915002</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1531,104 +1531,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>앤티크짐</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>antiquegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1357-0064</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 광명시 양지로 19 유플래닛 어반브릭스 B동 433호 429호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/antiquegym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40e5k</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>343</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>388</v>
-      </c>
-      <c r="R12" t="n">
-        <v>731</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1638569769</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1638569769</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광명시 하안로288번길 15 조일프라자 5층</t>
+          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43k9f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기도 광명시 일직로12번길 22 라까사호텔 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/witsh32</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="Q3" t="n">
         <v>361</v>
       </c>
       <c r="R3" t="n">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcsoke</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="Q4" t="n">
         <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 992 12층 1201호</t>
+          <t>경기도 광명시 오리로 992 12층 1201호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4k4y2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 865 601호</t>
+          <t>경기도 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4y72y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 23 명산��딩 302호</t>
+          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c1ao</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1118,10 +1094,10 @@
         <v>572</v>
       </c>
       <c r="Q7" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="R7" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
+          <t>경기도 광명시 신기로 7 골드스타빌딩 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48j21</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1271,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 11 5층</t>
+          <t>경기도 광명시 오리로856번길 11 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1296,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgyxanj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1315,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q9" t="n">
         <v>485</v>
       </c>
       <c r="R9" t="n">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1365,7 +1333,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzcy70h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1441,96 +1405,186 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GYM101 헬스 PT 광명사거리역점</t>
+          <t>바디채움PT&amp;운동센터 하안점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gym101@naver.com</t>
+          <t>bodychaeum@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1330-3078</t>
+          <t>0507-1378-6854</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 광명시 광명로 841 B1층</t>
+          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>https://blog.naver.com/bodychaeum</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>167</v>
+      </c>
+      <c r="R11" t="n">
+        <v>229</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1473047975</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1473047975</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gym101@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1330-3078</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 841 B1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/gym101_gwangmyeong</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxgpr6n</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>407</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>409</v>
+      </c>
+      <c r="Q12" t="n">
         <v>259</v>
       </c>
-      <c r="R11" t="n">
-        <v>666</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="R12" t="n">
+        <v>668</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1261214988</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1261214988</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
+          <t>경기 광명시 하안로288번길 15 조일프라자 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43k9f</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="Q2" t="n">
         <v>342</v>
       </c>
       <c r="R2" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcsoke</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로 992 12층 1201호</t>
+          <t>경기 광명시 오리로 992 12층 1201호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k4y2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로 865 601호</t>
+          <t>경기 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4y72y</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1051,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c1ao</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1243,7 +1263,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로856번길 11 5층</t>
+          <t>경기 광명시 오리로856번길 11 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgyxanj</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q9" t="n">
         <v>485</v>
       </c>
       <c r="R9" t="n">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1333,7 +1357,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1358,10 +1382,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzcy70h</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디채움PT&amp;운동센터 하안점</t>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodychaeum@naver.com</t>
+          <t>gym101@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1378-6854</t>
+          <t>0507-1330-3078</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+          <t>경기 광명시 광명로 841 B1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychaeum</t>
+          <t>https://www.instagram.com/gym101_gwangmyeong</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1475,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxgpr6n</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62</v>
+        <v>409</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="R11" t="n">
-        <v>229</v>
+        <v>668</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1473047975</t>
+          <t>1261214988</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473047975</t>
+          <t>https://m.place.naver.com/place/1261214988</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,29 +1536,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GYM101 헬스 PT 광명사거리역점</t>
+          <t>핏클러스터 헬스&amp;그룹PT&amp;월요가</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gym101@naver.com</t>
+          <t>fit_cluster@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1330-3078</t>
+          <t>0507-1435-0817</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 광명시 광명로 841 B1층</t>
+          <t>경기도 광명시 양지로 19 유플래닛어반브릭스 B동 4층 403호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+          <t>https://blog.naver.com/fit_cluster</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1573,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>409</v>
+        <v>163</v>
       </c>
       <c r="Q12" t="n">
-        <v>259</v>
+        <v>650</v>
       </c>
       <c r="R12" t="n">
-        <v>668</v>
+        <v>813</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,15 +1608,109 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1261214988</t>
+          <t>1892925915</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261214988</t>
+          <t>https://m.place.naver.com/place/1892925915</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>벨로짐 PT전문 광명역점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>maniastory25@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1374-7724</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 광명시 신기로 15 S프라자 7동 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/maniastory25</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>118</v>
+      </c>
+      <c r="R13" t="n">
+        <v>226</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1079640498</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1079640498</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,39 +564,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스엠 헬스&amp;pt 하안점</t>
+          <t>나우메이드 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessm10@naver.com</t>
+          <t>nowmade_fitness1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1444-0167</t>
+          <t>0507-1391-7883</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광명시 하안로288번길 15 조일프라자 5층</t>
+          <t>경기도 광명시 오리로 856 B2층,B3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AZJAG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43k9f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1613</v>
+        <v>584</v>
       </c>
       <c r="Q2" t="n">
-        <v>342</v>
+        <v>491</v>
       </c>
       <c r="R2" t="n">
-        <v>1955</v>
+        <v>1075</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20076918</t>
+          <t>1003902083</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20076918</t>
+          <t>https://m.place.naver.com/place/1003902083</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인스타짐 광명역점</t>
+          <t>프라이드 핏</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>instargymgm@naver.com</t>
+          <t>pride_fit@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1436-8069</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기도 광명시 하안로287번길 22 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instargym_gm/</t>
+          <t>https://instagram.com/pride_fit_2017</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -719,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>896</v>
+        <v>38</v>
       </c>
       <c r="Q3" t="n">
-        <v>361</v>
+        <v>239</v>
       </c>
       <c r="R3" t="n">
-        <v>1257</v>
+        <v>277</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,51 +726,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1471490398</t>
+          <t>767500491</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471490398</t>
+          <t>https://m.place.naver.com/place/767500491</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>클리어짐 철산역점</t>
+          <t>케이바디휘트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cleargym@naver.com</t>
+          <t>kstkbody@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1371-1045</t>
+          <t>0507-1476-8009</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기도 광명시 도덕공원로 23 서빈빌딩 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +780,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,27 +795,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsoke</t>
+          <t>https://talk.naver.com/ct/w97svnl</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1919</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
-        <v>624</v>
+        <v>169</v>
       </c>
       <c r="R4" t="n">
-        <v>2543</v>
+        <v>210</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1477285733</t>
+          <t>34129933</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477285733</t>
+          <t>https://m.place.naver.com/place/34129933</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디채널&amp;바레톤 광명사거리역점</t>
+          <t>짐타임피트니스 광명점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodychannelg@naver.com</t>
+          <t>alltimegym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1419-4015</t>
+          <t>0507-1378-0923</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 992 12층 1201호</t>
+          <t>경기도 광명시 광명로 829 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannelg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +893,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4k4y2</t>
+          <t>https://talk.naver.com/ct/wc5wirw</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>442</v>
+        <v>250</v>
       </c>
       <c r="Q5" t="n">
-        <v>1672</v>
+        <v>1117</v>
       </c>
       <c r="R5" t="n">
-        <v>2114</v>
+        <v>1367</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1349719442</t>
+          <t>1053542797</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349719442</t>
+          <t>https://m.place.naver.com/place/1053542797</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -952,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 철산점</t>
+          <t>코리아 피티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboycs@naver.com</t>
+          <t>korea-pt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1427-8902</t>
+          <t>0507-1383-7745</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 865 601호</t>
+          <t>경기도 광명시 양지로 21 유플래닛 티타워동 806호~811호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboycs/223877855300</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +976,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +991,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4y72y</t>
+          <t>https://talk.naver.com/ct/w4b3zc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>663</v>
+        <v>124</v>
       </c>
       <c r="Q6" t="n">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="R6" t="n">
-        <v>1108</v>
+        <v>555</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1197140079</t>
+          <t>1108205453</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197140079</t>
+          <t>https://m.place.naver.com/place/1108205453</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>무브데이 PT 광명철산점</t>
+          <t>일루고짐&amp;PT 하안점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>moveday01@naver.com</t>
+          <t>illugowoo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-1693</t>
+          <t>0507-1393-1430</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기도 광명시 안현로 51 3층 일루고짐&amp;PT 하안점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/moveday01/223721875157</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1074,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c1ao</t>
+          <t>https://talk.naver.com/ct/w5ix7r</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>572</v>
+        <v>159</v>
       </c>
       <c r="Q7" t="n">
-        <v>749</v>
+        <v>269</v>
       </c>
       <c r="R7" t="n">
-        <v>1321</v>
+        <v>428</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1118,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1505993596</t>
+          <t>1747199272</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505993596</t>
+          <t>https://m.place.naver.com/place/1747199272</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>클리어짐 광명역점</t>
+          <t>퍼스트라인팀</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cleargym2@naver.com</t>
+          <t>tongee115@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1342-0538</t>
+          <t>0507-1334-7902</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 광명시 신기로 7 골드스타빌딩 7층</t>
+          <t>경기도 광명시 광명역로 28 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,12 +1172,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1201,17 +1193,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>961</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>247</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1208</v>
+        <v>3</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,100 +1212,92 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1099783664</t>
+          <t>1112785214</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099783664</t>
+          <t>https://m.place.naver.com/place/1112785214</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>전문건설업</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 철산점</t>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-2625-3912</t>
+          <t>070-8055-3971</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 11 5층</t>
+          <t>경기도 광명시 하안동</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://fitnesspeople.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgyxanj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1239968125</t>
+          <t>1352062282</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239968125</t>
+          <t>https://m.place.naver.com/place/1352062282</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1344,25 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔짐 철산점</t>
+          <t>업투 광명소하점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ngym_cs@naver.com</t>
+          <t>uptofitness04@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1370-1445</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기도 광명시 하안로 108 302호, 303호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ngym_cs</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1360,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzcy70h</t>
+          <t>https://talk.naver.com/ct/wqskmf5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>190</v>
+        <v>447</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2058915002</t>
+          <t>1229526677</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058915002</t>
+          <t>https://m.place.naver.com/place/1229526677</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1426,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GYM101 헬스 PT 광명사거리역점</t>
+          <t>뉴짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gym101@naver.com</t>
+          <t>skyofmilk@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1330-3078</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 광명시 광명로 841 B1층</t>
+          <t>경기도 광명시 양지로 11 유-스트리트몰 104호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,7 +1454,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1485,27 +1469,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxgpr6n</t>
+          <t>https://talk.naver.com/ct/wmjl0nl</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>409</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="R11" t="n">
-        <v>668</v>
+        <v>284</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1498,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1261214988</t>
+          <t>1123876171</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261214988</t>
+          <t>https://m.place.naver.com/place/1123876171</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1536,29 +1520,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>핏클러스터 헬스&amp;그룹PT&amp;월요가</t>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fit_cluster@naver.com</t>
+          <t>gym101@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1435-0817</t>
+          <t>0507-1330-3078</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 광명시 양지로 19 유플래닛어반브릭스 B동 4층 403호</t>
+          <t>경기도 광명시 광명로 841 B1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fit_cluster</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,20 +1552,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxgpr6n</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1593,13 +1581,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>163</v>
+        <v>409</v>
       </c>
       <c r="Q12" t="n">
-        <v>650</v>
+        <v>259</v>
       </c>
       <c r="R12" t="n">
-        <v>813</v>
+        <v>668</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,111 +1596,8097 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1892925915</t>
+          <t>1261214988</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892925915</t>
+          <t>https://m.place.naver.com/place/1261214988</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>벨로짐 PT전문 광명역점</t>
+          <t>프라임짐 헬스 PT 광명사거리역점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>maniastory25@naver.com</t>
+          <t>primegym3@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1374-7724</t>
+          <t>0507-1339-2581</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>경기도 광명시 오리로 986 6층 1호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/primegym4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdcabj7</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>675</v>
+      </c>
+      <c r="R13" t="n">
+        <v>908</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2032025487</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032025487</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>인싸짐 소하점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dlsfbf6158@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1425-3818</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 378 5층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we5lw3q</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>422</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>562</v>
+      </c>
+      <c r="R14" t="n">
+        <v>984</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1624195066</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1624195066</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>헬스보이짐 철산점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>healthboycs@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1427-8902</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 865 601호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboycs/223877855300</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>445</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1197140079</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197140079</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>포그로스PT&amp;필라테스 광명하안점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pogrowth3@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1342-2306</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 258 경향빌딩 301호 포그로스</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zpbt</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>268</v>
+      </c>
+      <c r="R16" t="n">
+        <v>449</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1853155044</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853155044</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>원픽짐PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>onepickgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1328-1446</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 광명시 시청로 50 롯데캐슬&amp;SK뷰상가 프라자 B동 202호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ay8p</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>134</v>
+      </c>
+      <c r="R17" t="n">
+        <v>497</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1142090110</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1142090110</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>올핏</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>allfit92@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 309 5층 502호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ynvc</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>178</v>
+      </c>
+      <c r="R18" t="n">
+        <v>285</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1335849285</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1335849285</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>여성전용 헬스&amp;PT 엔젤피트니스</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>angelfitness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1369-9061</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 293-10 6층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wck5lvy</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>311</v>
+      </c>
+      <c r="R19" t="n">
+        <v>640</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1362826765</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1362826765</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>리부트 팀트레이닝</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>reborn_bootcamp_01@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02-2682-2228</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 20 야우리빌딩 4층 403호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://www.reborn-bootcamp.com/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>344</v>
+      </c>
+      <c r="R20" t="n">
+        <v>546</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1066371237</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1066371237</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>머스타드피트니스 철산역점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mustardfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1414-7199</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 20 야우리빌딩 10층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://www.mustard-fitness.com/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43cl1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1549</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>205</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1754</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>12762047</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12762047</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>인스타짐 광명역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>instargymgm@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1436-8069</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 광명시 일직로12번길 22 라까사호텔 3층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/witsh32</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>361</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1257</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1471490398</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1471490398</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>이엘피티 광명철산점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sohapilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1361-0157</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로33번길 5 그랜드 프라자 4층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43lj5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>243</v>
+      </c>
+      <c r="R23" t="n">
+        <v>278</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1799161803</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799161803</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>스마일휘트니스 헬스&amp;PT 소하점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>smile_fitness_soha@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02-899-5249</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 351 동림프라자 5층 스마일 휘트니스</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>115</v>
+      </c>
+      <c r="R24" t="n">
+        <v>235</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>12815627</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12815627</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>브이브이에스짐 헬스&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>vvsgym1011@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1387-0236</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 295 노벨빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>527</v>
+      </c>
+      <c r="R25" t="n">
+        <v>786</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1223362090</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223362090</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>클리어짐 철산역점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cleargym@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1371-1045</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcsoke</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1919</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>624</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2543</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1477285733</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1477285733</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>070-8914-1681</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명7동</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1646833483</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646833483</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>앤티크짐</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>antiquegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1357-0064</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 광명시 양지로 19 유플래닛 어반브릭스 B동 433호 429호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40e5k</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>388</v>
+      </c>
+      <c r="R28" t="n">
+        <v>731</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1638569769</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1638569769</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>지앤지휘트니스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ghdavil@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>02-897-9599</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 315 한일빌딩</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>225</v>
+      </c>
+      <c r="R29" t="n">
+        <v>238</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>36481493</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36481493</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>척추,자세교정</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>한걸음재활운동센터</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>manualtherapy1@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1388-4250</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 광명시 신기로 7 5층 502호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>30</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2056960629</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2056960629</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>밸런스PT센터</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>balancept_@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1300-6724</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하로109번길 24 3층 302호(소하동) 밸런스PT센터</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46uhn</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>368</v>
+      </c>
+      <c r="R31" t="n">
+        <v>456</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1493639893</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1493639893</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>킥복싱</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>황gym</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sna0413@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>02-2616-1774</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 858 3층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>50</v>
+      </c>
+      <c r="R32" t="n">
+        <v>75</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>37630186</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37630186</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>위무브트레이닝</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>we_move_training1350@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 20 지하 2층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/web1ock</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>249</v>
+      </c>
+      <c r="R33" t="n">
+        <v>292</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2053267274</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053267274</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>팀식스짐 소하점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>teamsixgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1427-2248</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 464 509호 팀식스짐</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e3m1</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>110</v>
+      </c>
+      <c r="R34" t="n">
+        <v>168</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>482614696</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/482614696</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT 소하점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hwklee1989@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1346-9220</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하로 88 청학프라자 3층 터닝포인트짐</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/turningpointgym_soha</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>552</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1098</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>32547976</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32547976</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>070-8914-6613</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 광명시 옥길동</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1846363978</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846363978</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>코우짐</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>caugym@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1327-5333</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 광명시 일직로 43 GIDC A동 1층 1023호 코우짐</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e6xq</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>210</v>
+      </c>
+      <c r="R37" t="n">
+        <v>412</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1066577339</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1066577339</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>클리어짐 광명역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cleargym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1342-0538</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 광명시 신기로 7 골드스타빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48j21</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>961</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>247</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1208</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1099783664</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099783664</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GYMS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>gyms_fitin365@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1341-6889</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 광명시 모세로 40 지하1층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>82</v>
+      </c>
+      <c r="R39" t="n">
+        <v>82</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1206907014</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206907014</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>짐샤크 헬스&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>gymshark01@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1348-5703</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 289 태홍빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4777f</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1013</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>296</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1309</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1881875836</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1881875836</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>탑핏30 광명하안점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>topfit30_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 13 계명빌딩 502호 탑핏30 광명 하안점</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b28q</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>30</v>
+      </c>
+      <c r="R41" t="n">
+        <v>43</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1198319775</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198319775</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>광명 위너복싱</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>winnerboxing_@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>02-2688-3557</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 광명시 도덕로 39 5층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>121</v>
+      </c>
+      <c r="R42" t="n">
+        <v>152</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1982987316</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1982987316</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>아놀드짐 ARNOLDGYM PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>youand1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02-2612-3111</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 943 3층 아놀드GYM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>30</v>
+      </c>
+      <c r="R43" t="n">
+        <v>61</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>17884074</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17884074</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>070-8055-4013</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하동</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1692881247</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692881247</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>영어교육</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>더영어PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>the_english_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1459-4312</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 광명시 일직로 43 C동 11층 1106호 MERI 세미나실</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1970648161</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970648161</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>아크 피티&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>rapper0808@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1348-6207</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하로76번길 7 우심프라자6층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcd5ye</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>188</v>
+      </c>
+      <c r="R46" t="n">
+        <v>207</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1191631636</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1191631636</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>이안짐</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>iamgym_story@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1334-5697</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 529 비엔팰리스 404호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1143525481</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1143525481</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>요가원</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>마인드힐 필라테스&amp;월요가PT 광명철산점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mindheal_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1345-1538</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로33번길 5 그랜드프라자 404호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ls56</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>278</v>
+      </c>
+      <c r="R48" t="n">
+        <v>466</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1602735469</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1602735469</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>피지스 피지컬트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>phyzis@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1331-1177</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로651번길 5 501호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/phyzis</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>29</v>
+      </c>
+      <c r="R49" t="n">
+        <v>29</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1548977040</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1548977040</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>무브데이 PT 광명철산점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>moveday01@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1349-1693</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c1ao</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>573</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>749</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1322</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1505993596</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1505993596</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>리본필라테스 광명철산점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>reborn_gusnak@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>hello@rebornpilates.com</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02-2617-2227</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로 13 한국빌딩 6F</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>http://www.rebornpilates.com/cheolsan_studio</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4nw79</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>587</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2745</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3332</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>37039232</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37039232</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>하데스클럽 광명하안점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>tina09now@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1307-7359</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 광명시 범안로 1055 10층 전관</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wac1b45</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>30</v>
+      </c>
+      <c r="R52" t="n">
+        <v>47</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2091152989</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2091152989</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>라잇나우짐</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>rightnowgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02-898-5382</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 233 4층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://gorightnowgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wsnt</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>39</v>
+      </c>
+      <c r="R53" t="n">
+        <v>108</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1811074473</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1811074473</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>핏클러스터 헬스&amp;그룹PT&amp;월요가</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fit_cluster@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1435-0817</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 광명시 양지로 19 유플래닛어반브릭스 B동 4층 403호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fit_cluster</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>650</v>
+      </c>
+      <c r="R54" t="n">
+        <v>813</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1892925915</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1892925915</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>일루고짐&amp;PT 소하점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>soobin_1992@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1359-2531</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 526 농협건물 2층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t0wd</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>131</v>
+      </c>
+      <c r="R55" t="n">
+        <v>313</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1800433585</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800433585</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>캐리짐</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>carrygym_kim@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 광명시 새빛공원로 67 B동 314호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mqng</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>103</v>
+      </c>
+      <c r="R56" t="n">
+        <v>146</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1932319960</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932319960</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>에이오짐 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>fitnessdive@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1348-1603</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로29번길 5 은성빌딩 지층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fo0s</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>393</v>
+      </c>
+      <c r="R57" t="n">
+        <v>575</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1309466972</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1309466972</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>070-8914-4524</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하2동</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1741252859</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1741252859</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 철산점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>02-2625-3912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로856번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://fitnesspeople.co.kr/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>464</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>485</v>
+      </c>
+      <c r="R59" t="n">
+        <v>949</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1239968125</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1239968125</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>피트니스153</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fitness153pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1428-1531</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 200 스페이스빌딩 5층 501호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uev9</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>15</v>
+      </c>
+      <c r="R60" t="n">
+        <v>37</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1387533165</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1387533165</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>드림 헬스&amp;PT 광명역점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>kkuy0106@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1367-3192</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 광명시 일직로12번길 24 5층 501호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt0q3if</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>135</v>
+      </c>
+      <c r="R61" t="n">
+        <v>219</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2005243970</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2005243970</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>나인투짐 광명점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ninetwogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1353-2426</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 1005 2층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4s26j</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>192</v>
+      </c>
+      <c r="R62" t="n">
+        <v>255</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1485760457</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1485760457</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>렛츠핏 하안점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>letsfithaan@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1339-0298</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 314 2층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://bmarket.broj.co.kr/groups/373166261</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49d26</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>770</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>899</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1669</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1590511442</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1590511442</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>엔짐 철산점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ngym_cs@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzcy70h</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>46</v>
+      </c>
+      <c r="R64" t="n">
+        <v>190</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2058915002</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058915002</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>더스페이스짐</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>alth1533@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>02-2613-3911</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 907 6층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://thespacegym.imweb.me/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>17</v>
+      </c>
+      <c r="R65" t="n">
+        <v>214</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1531212434</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1531212434</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>캐리피트니스</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>carrygym_kim@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1438-1567</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 광명시 새빛공원로 67 A동 지하1층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>3</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1251065843</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251065843</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>짐고잉 헬스&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gymgoing@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1336-5596</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 광명시 범안로 1056 701호, 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymgoing</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>818</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>379</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1197</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1687174872</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1687174872</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>초이스짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>choice-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1327-9698</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 광명시 서독로 392 광명역D환승주차장 3층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hfr6</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>712</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>175</v>
+      </c>
+      <c r="R68" t="n">
+        <v>887</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1025902553</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025902553</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>바디채움PT&amp;운동센터 하안점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bodychaeum@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1378-6854</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wlkbwl8</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>167</v>
+      </c>
+      <c r="R69" t="n">
+        <v>229</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1473047975</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1473047975</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>써니업 여성맞춤 피트니스 광명하안점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sunnyupfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>02-6956-0202</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 9 4층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yvoj</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>177</v>
+      </c>
+      <c r="R70" t="n">
+        <v>313</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1046530777</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046530777</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>고하드짐 헬스PT 광명하안점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>go_hard_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1409-2438</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 293-12 대인빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ab8y</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>365</v>
+      </c>
+      <c r="R71" t="n">
+        <v>542</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1338500962</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338500962</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>운동노리</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>noricare_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1404-7529</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로30번길 24 303호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fe0g</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>5</v>
+      </c>
+      <c r="R72" t="n">
+        <v>11</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1029915219</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1029915219</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>충남가설재</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dgdg004@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>02-2684-8778</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 광명시 옥길동 236-2</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://www.cn26048778.co.kr/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
+        <v>12</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>12877808</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12877808</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>바디마인퍼스널트레이닝 2호점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>bodymine2@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>02-2611-2202</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 12 5층 501호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5v8</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>113</v>
+      </c>
+      <c r="R74" t="n">
+        <v>187</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1891984160</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1891984160</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>에스엔티스포츠</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>snt_sports@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1318-7399</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 광명시 신기로17번길 11 4층 406호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4epzc</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>87</v>
+      </c>
+      <c r="R75" t="n">
+        <v>119</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1337144289</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1337144289</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>피티아시바,비티아시바파이프,토류판,유로폼,가설자재임대판매</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>zizoiop@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>070-5258-4099</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 광명시 옥길동</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1294945654</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1294945654</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>피티아시바,비티아시바파이프,토류판,유로폼,가설자재임대판매</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>zizoiop@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>070-5258-6828</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명동</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1727045581</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1727045581</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>바디채널&amp;바레톤 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>bodychannelg@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1419-4015</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 992 12층 1201호</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k4y2</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1672</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2114</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1349719442</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349719442</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>휘트니스엠 헬스&amp;pt 하안점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>fitnessm10@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1444-0167</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43k9f</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>1613</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>342</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1955</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>20076918</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20076918</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>원앤온리짐 광명철산점</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>one_and_only_gym_cs@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1465-8312</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로 17 3층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41agt</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>197</v>
+      </c>
+      <c r="R80" t="n">
+        <v>423</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1499783974</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1499783974</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>철산Jin복싱클럽</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yangky0714@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1386-8000</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 25 B1층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/jin_boxing_info</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcb18t</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>333</v>
+      </c>
+      <c r="R81" t="n">
+        <v>394</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>12048302</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12048302</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>하프타임 PT &amp; 축구</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>halftime_@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1355-2807</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>경기도 광명시 도덕공원로 27 지하1층</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xl3k</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>7</v>
+      </c>
+      <c r="R82" t="n">
+        <v>20</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1854620290</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1854620290</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>바른PT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>motionck123@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1435-0616</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광덕산로 5 지하1층 101호 바른pt</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>39</v>
+      </c>
+      <c r="R83" t="n">
+        <v>44</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>37213704</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37213704</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 광명하안점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1345-6406</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 258 B1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=45</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>1040</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>88</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1128</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1251840390</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251840390</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>벨로짐 PT전문 광명역점</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>maniastory25@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1374-7724</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
           <t>경기도 광명시 신기로 15 S프라자 7동 703호, 704호</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>https://blog.naver.com/maniastory25</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
         <v>108</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q85" t="n">
         <v>118</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R85" t="n">
         <v>226</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
         <is>
           <t>1079640498</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1079640498</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>학원 등 교습시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>피티수학영어학원</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>greenpcs@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1407-6653</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광복로 66-1 1층 104호</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>13</v>
+      </c>
+      <c r="R86" t="n">
+        <v>13</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1071133069</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1071133069</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 철산점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1336-6406</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 857 지하1층 짐박스피트니스</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=49</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>704</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>104</v>
+      </c>
+      <c r="R87" t="n">
+        <v>808</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1933756441</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1933756441</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>휴먼시아휘트니스</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>saray78@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02-897-0693</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>경기도 광명시 성채로 36 휴먼시아 3단지아파트 306동</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>18</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>621408193</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/621408193</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>결대로 방문재활운동센터</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ptleehome@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1381-6971</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>경기도 광명시 사성로103번길 14 광복현대아파트 106동 509호</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>111</v>
+      </c>
+      <c r="R89" t="n">
+        <v>111</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2092174117</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2092174117</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>광명SK테크노파크휘트니스</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>skfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>02-898-1003</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 60 광명SK테크노파크 Biz tower 3층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/skfit</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>39</v>
+      </c>
+      <c r="R90" t="n">
+        <v>115</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>34984276</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34984276</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>일루고짐&amp;PT 철산점</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>hyunwoo6333@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1366-5055</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>경기도 광명시 도덕공원로 59 광명 푸르지오 상가 2층 일루고짐</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u19s</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>152</v>
+      </c>
+      <c r="R91" t="n">
+        <v>374</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1210994452</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1210994452</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 광명점</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02-2613-3912</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 907 광명빌딩 7층 휘트니스피플</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42ig4</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>1675</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>666</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2341</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>38321449</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38321449</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>뱅가드 피트니스 24시 광명점</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>vgfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1387-5335</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광화로 22 로얄프라자 지하1층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d955</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>77</v>
+      </c>
+      <c r="R93" t="n">
+        <v>384</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1021155109</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1021155109</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>바디토크짐</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>syk3545@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>경기도 광명시 기아로 56 5층</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>24</v>
+      </c>
+      <c r="R94" t="n">
+        <v>31</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1294969113</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1294969113</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>엠핏운동센터</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>mfit2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 649 경일빌딩 403호</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>101</v>
+      </c>
+      <c r="R95" t="n">
+        <v>108</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1219341151</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219341151</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>벨로짐 PT&amp;스트레치 광명소하점</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>bellogym_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1339-0161</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 458 웅신아트 304호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://bellogym.kr</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>304</v>
+      </c>
+      <c r="R96" t="n">
+        <v>490</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1250323460</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250323460</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="Q4" t="n">
         <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>442</v>
       </c>
       <c r="Q5" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="R5" t="n">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Q8" t="n">
         <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q9" t="n">
         <v>485</v>
       </c>
       <c r="R9" t="n">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GYM101 헬스 PT 광명사거리역점</t>
+          <t>바디채움PT&amp;운동센터 하안점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gym101@naver.com</t>
+          <t>bodychaeum@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1330-3078</t>
+          <t>0507-1378-6854</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 광명시 광명로 841 B1층</t>
+          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+          <t>https://blog.naver.com/bodychaeum</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,30 +1467,124 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>167</v>
+      </c>
+      <c r="R11" t="n">
+        <v>229</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1473047975</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1473047975</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gym101@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1330-3078</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 841 B1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>409</v>
       </c>
-      <c r="Q11" t="n">
-        <v>259</v>
-      </c>
-      <c r="R11" t="n">
-        <v>668</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>261</v>
+      </c>
+      <c r="R12" t="n">
+        <v>670</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1261214988</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1261214988</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스엠 헬스&amp;pt 하안점</t>
+          <t>인스타짐 광명역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessm10@naver.com</t>
+          <t>instargymgm@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1444-0167</t>
+          <t>0507-1436-8069</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
+          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AZJAG</t>
+          <t>https://www.instagram.com/instargym_gm/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/witsh32</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1613</v>
+        <v>896</v>
       </c>
       <c r="Q2" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="R2" t="n">
-        <v>1955</v>
+        <v>1257</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,47 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20076918</t>
+          <t>1471490398</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20076918</t>
+          <t>https://m.place.naver.com/place/1471490398</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인스타짐 광명역점</t>
+          <t>헬스엔젤스필라테스 광명점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>instargymgm@naver.com</t>
+          <t>haelthangels11@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1436-8069</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기 광명시 범안로 1049 성원빌딩 6층 제1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instargym_gm/</t>
+          <t>https://blog.naver.com/haelthangels11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +695,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa8uero</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>896</v>
+        <v>219</v>
       </c>
       <c r="Q3" t="n">
-        <v>361</v>
+        <v>53</v>
       </c>
       <c r="R3" t="n">
-        <v>1257</v>
+        <v>272</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1471490398</t>
+          <t>1102369380</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471490398</t>
+          <t>https://m.place.naver.com/place/1102369380</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcsoke</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="Q4" t="n">
         <v>624</v>
       </c>
       <c r="R4" t="n">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로 992 12층 1201호</t>
+          <t>경기 광명시 오리로 992 12층 1201호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k4y2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q5" t="n">
         <v>1673</v>
       </c>
       <c r="R5" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로 865 601호</t>
+          <t>경기 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4y72y</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1022,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4c1ao</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q7" t="n">
         <v>749</v>
       </c>
       <c r="R7" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 광명시 신기로 7 골드스타빌딩 7층</t>
+          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48j21</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="Q8" t="n">
         <v>247</v>
       </c>
       <c r="R8" t="n">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 광명시 오리로856번길 11 5층</t>
+          <t>경기 광명시 오리로856번길 11 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgyxanj</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1308,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1361,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1358,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzcy70h</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1398,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1459,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+          <t>경기 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1452,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wlkbwl8</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q11" t="n">
         <v>167</v>
       </c>
       <c r="R11" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1492,41 +1528,41 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GYM101 헬스 PT 광명사거리역점</t>
+          <t>밸런스PT센터</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gym101@naver.com</t>
+          <t>balancept_@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1330-3078</t>
+          <t>0507-1300-6724</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 광명시 광명로 841 B1층</t>
+          <t>경기 광명시 소하로109번길 24 3층 302호(소하동) 밸런스PT센터</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+          <t>https://blog.naver.com/balancept_</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,15 +1577,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46uhn</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>409</v>
+        <v>88</v>
       </c>
       <c r="Q12" t="n">
-        <v>261</v>
+        <v>368</v>
       </c>
       <c r="R12" t="n">
-        <v>670</v>
+        <v>456</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1261214988</t>
+          <t>1493639893</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261214988</t>
+          <t>https://m.place.naver.com/place/1493639893</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>인스타짐 광명역점</t>
+          <t>케이바디휘트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>instargymgm@naver.com</t>
+          <t>kstkbody@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-8069</t>
+          <t>0507-1476-8009</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기도 광명시 도덕공원로 23 서빈빌딩 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instargym_gm/</t>
+          <t>https://blog.naver.com/kstkbody</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,37 +601,33 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/witsh32</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>896</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="n">
-        <v>361</v>
+        <v>169</v>
       </c>
       <c r="R2" t="n">
-        <v>1257</v>
+        <v>210</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1471490398</t>
+          <t>34129933</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471490398</t>
+          <t>https://m.place.naver.com/place/34129933</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,30 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스엔젤스필라테스 광명점</t>
+          <t>인싸짐 소하점 헬스 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>haelthangels11@naver.com</t>
+          <t>dlsfbf6158@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1425-3818</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 광명시 범안로 1049 성원빌딩 6층 제1호</t>
+          <t>경기도 광명시 오리로 378 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/haelthangels11</t>
+          <t>https://blog.naver.com/dlsfbf6158</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa8uero</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>219</v>
+        <v>422</v>
       </c>
       <c r="Q3" t="n">
-        <v>53</v>
+        <v>562</v>
       </c>
       <c r="R3" t="n">
-        <v>272</v>
+        <v>984</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1102369380</t>
+          <t>1624195066</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102369380</t>
+          <t>https://m.place.naver.com/place/1624195066</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>클리어짐 철산역점</t>
+          <t>헬스보이짐 철산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cleargym@naver.com</t>
+          <t>healthboycs@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1371-1045</t>
+          <t>0507-1427-8902</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+          <t>경기도 광명시 오리로 865 601호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym</t>
+          <t>https://blog.naver.com/healthboycs/223877855300</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcsoke</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1921</v>
+        <v>664</v>
       </c>
       <c r="Q4" t="n">
-        <v>624</v>
+        <v>445</v>
       </c>
       <c r="R4" t="n">
-        <v>2545</v>
+        <v>1109</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1477285733</t>
+          <t>1197140079</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477285733</t>
+          <t>https://m.place.naver.com/place/1197140079</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디채널&amp;바레톤 광명사거리역점</t>
+          <t>GYMS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodychannelg@naver.com</t>
+          <t>gyms_fitin365@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1419-4015</t>
+          <t>0507-1341-6889</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 992 12층 1201호</t>
+          <t>경기도 광명시 모세로 40 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychannelg</t>
+          <t>https://blog.naver.com/gyms_fitin365</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4k4y2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1673</v>
+        <v>82</v>
       </c>
       <c r="R5" t="n">
-        <v>2116</v>
+        <v>82</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1349719442</t>
+          <t>1206907014</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1349719442</t>
+          <t>https://m.place.naver.com/place/1206907014</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,34 +935,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>킥복싱</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 철산점</t>
+          <t>황gym</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboycs@naver.com</t>
+          <t>sna0413@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1427-8902</t>
+          <t>02-2616-1774</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로 865 601호</t>
+          <t>경기도 광명시 광명로 858 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboycs/223877855300</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4y72y</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>663</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>445</v>
+        <v>50</v>
       </c>
       <c r="R6" t="n">
-        <v>1108</v>
+        <v>75</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1197140079</t>
+          <t>37630186</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197140079</t>
+          <t>https://m.place.naver.com/place/37630186</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1045,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>무브데이 PT 광명철산점</t>
+          <t>휘트니스피플 우먼 광명점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>moveday01@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-1693</t>
+          <t>02-2613-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 23 명산빌딩 302호</t>
+          <t>경기도 광명시 광명로 907 광명빌딩 7층 휘트니스피플</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/moveday01/223721875157</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1092,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4c1ao</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>574</v>
+        <v>1677</v>
       </c>
       <c r="Q7" t="n">
-        <v>749</v>
+        <v>666</v>
       </c>
       <c r="R7" t="n">
-        <v>1323</v>
+        <v>2343</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1505993596</t>
+          <t>38321449</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1505993596</t>
+          <t>https://m.place.naver.com/place/38321449</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>클리어짐 광명역점</t>
+          <t>인스타짐 광명역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cleargym2@naver.com</t>
+          <t>instargymgm@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1342-0538</t>
+          <t>0507-1436-8069</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
+          <t>경기도 광명시 일직로12번길 22 라까사호텔 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cleargym2</t>
+          <t>https://www.instagram.com/instargym_gm/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,19 +1165,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48j21</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="Q8" t="n">
-        <v>247</v>
+        <v>363</v>
       </c>
       <c r="R8" t="n">
-        <v>1211</v>
+        <v>1259</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1099783664</t>
+          <t>1471490398</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099783664</t>
+          <t>https://m.place.naver.com/place/1471490398</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,38 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 철산점</t>
+          <t>뱅가드 피트니스 24시 광명점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>psi@fitnesspeople.co.kr</t>
-        </is>
-      </c>
+          <t>vgfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-2625-3912</t>
+          <t>0507-1387-5335</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 광명시 오리로856번길 11 5층</t>
+          <t>경기도 광명시 광화로 22 로얄프라자 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://fitnesspeople.co.kr/</t>
+          <t>https://smartstore.naver.com/vgfitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,22 +1259,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgyxanj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>466</v>
+        <v>307</v>
       </c>
       <c r="Q9" t="n">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="R9" t="n">
-        <v>951</v>
+        <v>385</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1239968125</t>
+          <t>1021155109</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239968125</t>
+          <t>https://m.place.naver.com/place/1021155109</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,30 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔짐 철산점</t>
+          <t>포그로스PT&amp;필라테스 광명하안점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ngym_cs@naver.com</t>
+          <t>pogrowth3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1342-2306</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 광명시 시청로 139 우성아파트 상가 B1층</t>
+          <t>경기도 광명시 하안로 258 경향빌딩 301호 포그로스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ngym_cs</t>
+          <t>https://www.instagram.com/pogrowth_pilates/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,19 +1353,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzcy70h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>268</v>
       </c>
       <c r="R10" t="n">
-        <v>190</v>
+        <v>449</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2058915002</t>
+          <t>1853155044</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058915002</t>
+          <t>https://m.place.naver.com/place/1853155044</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디채움PT&amp;운동센터 하안점</t>
+          <t>일루고짐&amp;PT 철산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodychaeum@naver.com</t>
+          <t>hyunwoo6333@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1378-6854</t>
+          <t>0507-1366-5055</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+          <t>경기도 광명시 도덕공원로 59 광명 푸르지오 상가 2층 일루고짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodychaeum</t>
+          <t>https://blog.naver.com/hyunwoo6333</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wlkbwl8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>63</v>
+        <v>223</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="R11" t="n">
-        <v>230</v>
+        <v>375</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1473047975</t>
+          <t>1210994452</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473047975</t>
+          <t>https://m.place.naver.com/place/1210994452</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1540,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>밸런스PT센터</t>
+          <t>클리어짐 광명역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>balancept_@naver.com</t>
+          <t>cleargym2@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1300-6724</t>
+          <t>0507-1342-0538</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 광명시 소하로109번길 24 3층 302호(소하동) 밸런스PT센터</t>
+          <t>경기도 광명시 신기로 7 골드스타빌딩 7층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balancept_</t>
+          <t>https://blog.naver.com/cleargym2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1582,49 +1546,6835 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>964</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>247</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1211</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1099783664</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1099783664</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>원앤온리짐 광명철산점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>one_and_only_gym_cs@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1465-8312</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로 17 3층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/one_and_only_gym_cs</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>197</v>
+      </c>
+      <c r="R13" t="n">
+        <v>423</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1499783974</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1499783974</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>엠핏운동센터</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mfit2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 649 경일빌딩 403호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mfit2020</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>101</v>
+      </c>
+      <c r="R14" t="n">
+        <v>108</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1219341151</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219341151</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>리부트 팀트레이닝</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>reborn_bootcamp_01@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02-2682-2228</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 20 야우리빌딩 4층 403호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://www.reborn-bootcamp.com/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>344</v>
+      </c>
+      <c r="R15" t="n">
+        <v>546</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1066371237</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1066371237</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>요가원</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>마인드힐 필라테스&amp;월요가PT 광명철산점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mindheal_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1345-1538</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로33번길 5 그랜드프라자 404호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mindheal_studio</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>278</v>
+      </c>
+      <c r="R16" t="n">
+        <v>466</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1602735469</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1602735469</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>에이오짐 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fitnessdive@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1348-1603</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로29번길 5 은성빌딩 지층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/aogym_</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>575</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1309466972</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1309466972</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>앤티크짐</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>antiquegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1357-0064</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 광명시 양지로 19 유플래닛 어반브릭스 B동 433호 429호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/antiquegym</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>388</v>
+      </c>
+      <c r="R18" t="n">
+        <v>731</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1638569769</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1638569769</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>에스엔티스포츠</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>snt_sports@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1318-7399</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 광명시 신기로17번길 11 4층 406호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://naver.me/FUzh5KS6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>87</v>
+      </c>
+      <c r="R19" t="n">
+        <v>119</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1337144289</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1337144289</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gym101@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1330-3078</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 841 B1층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>410</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>262</v>
+      </c>
+      <c r="R20" t="n">
+        <v>672</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1261214988</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261214988</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>엔짐 철산점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ngym_cs@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 광명시 시청로 139 우성아파트 상가 B1층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ngym_cs</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>46</v>
+      </c>
+      <c r="R21" t="n">
+        <v>190</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2058915002</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058915002</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT 소하점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hwklee1989@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1346-9220</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하로 88 청학프라자 3층 터닝포인트짐</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/turningpointgym_soha</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>546</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>553</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1099</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>32547976</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32547976</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>일루고짐&amp;PT 소하점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>haon8312@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1359-2531</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 526 농협건물 2층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>131</v>
+      </c>
+      <c r="R23" t="n">
+        <v>313</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1800433585</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800433585</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>무브데이 PT 광명철산점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>moveday01@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1349-1693</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로856번길 23 명산빌딩 302호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moveday01/223721875157</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>574</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>750</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1324</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1505993596</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1505993596</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>이엘피티 광명철산점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sohapilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1361-0157</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로33번길 5 그랜드 프라자 4층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/el.pt_gym</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>243</v>
+      </c>
+      <c r="R25" t="n">
+        <v>278</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1799161803</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1799161803</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>초이스짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>choice-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1327-9698</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 광명시 서독로 392 광명역D환승주차장 3층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hfr6</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>713</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>181</v>
+      </c>
+      <c r="R26" t="n">
+        <v>894</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1025902553</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025902553</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>070-8914-1681</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명7동</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1646833483</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646833483</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>하데스클럽 광명하안점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>yyolooo@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1307-7359</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 광명시 범안로 1055 10층 전관</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wac1b45</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>37</v>
+      </c>
+      <c r="R28" t="n">
+        <v>54</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2091152989</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2091152989</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>피티아시바,비티아시바파이프,토류판,유로폼,가설자재임대판매</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>zizoiop@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>070-5258-6828</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명동</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1727045581</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1727045581</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 광명하안점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1345-6406</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 258 B1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=45</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1042</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>88</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1130</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1251840390</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251840390</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>올핏</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>allfit92@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 309 5층 502호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ynvc</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>178</v>
+      </c>
+      <c r="R31" t="n">
+        <v>285</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1335849285</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1335849285</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>코리아 피티</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>korea-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1383-7745</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 광명시 양지로 21 유플래닛 티타워동 806호~811호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b3zc</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>431</v>
+      </c>
+      <c r="R32" t="n">
+        <v>555</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1108205453</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1108205453</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>고하드짐 헬스PT 광명하안점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>go_hard_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1409-2438</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 293-12 대인빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ab8y</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>365</v>
+      </c>
+      <c r="R33" t="n">
+        <v>542</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1338500962</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338500962</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>브이브이에스짐 헬스&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>vvsgym1011@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1387-0236</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 295 노벨빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>527</v>
+      </c>
+      <c r="R34" t="n">
+        <v>786</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1223362090</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223362090</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>업투 광명소하점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>uptofitness04@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1370-1445</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 108 302호, 303호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uptofitness04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>386</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>62</v>
+      </c>
+      <c r="R35" t="n">
+        <v>448</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1229526677</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229526677</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>운동노리</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>noricare_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1404-7529</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로30번길 24 303호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/my/review/653f0af11dabc0d7260cfaa9</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>11</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1029915219</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1029915219</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>탑핏30 광명하안점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>lilianecosta@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 13 계명빌딩 502호 탑핏30 광명 하안점</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/topfit30_gwangmyeong</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>30</v>
+      </c>
+      <c r="R37" t="n">
+        <v>43</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1198319775</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198319775</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>바디채널&amp;바레톤 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bodychannelg@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1419-4015</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 992 12층 1201호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4k4y2</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>444</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1673</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2117</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1349719442</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349719442</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>나우메이드 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nowmade_fitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1391-7883</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 856 B2층,B3층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>588</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>496</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1084</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1003902083</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003902083</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>벨로짐 PT전문 광명역점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>maniastory25@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1374-7724</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 광명시 신기로 15 S프라자 7동 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bpjm</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>118</v>
+      </c>
+      <c r="R40" t="n">
+        <v>226</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1079640498</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1079640498</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>아크 피티&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>rapper0808@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1348-6207</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하로76번길 7 우심프라자6층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcd5ye</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>188</v>
+      </c>
+      <c r="R41" t="n">
+        <v>207</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1191631636</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1191631636</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>결대로 방문재활운동센터</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ptleehome@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1381-6971</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 광명시 사성로103번길 14 광복현대아파트 106동 509호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptleehome</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>112</v>
+      </c>
+      <c r="R42" t="n">
+        <v>112</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2092174117</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2092174117</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>이안짐</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>iamgym_story@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1334-5697</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 529 비엔팰리스 404호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1143525481</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1143525481</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>드림 헬스&amp;PT 광명역점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kkuy0106@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1367-3192</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 광명시 일직로12번길 24 5층 501호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt0q3if</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>135</v>
+      </c>
+      <c r="R44" t="n">
+        <v>219</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2005243970</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2005243970</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>하프타임 PT &amp; 축구</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>halftime_@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1355-2807</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 광명시 도덕공원로 27 지하1층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xl3k</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>7</v>
+      </c>
+      <c r="R45" t="n">
+        <v>20</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1854620290</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1854620290</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>여성전용 헬스&amp;PT 엔젤피트니스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>angelfitness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1369-9061</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 293-10 6층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wck5lvy</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>311</v>
+      </c>
+      <c r="R46" t="n">
+        <v>640</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1362826765</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1362826765</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>핏클러스터 헬스&amp;그룹PT&amp;월요가</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>fit_cluster@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1435-0817</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 광명시 양지로 19 유플래닛어반브릭스 B동 4층 403호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eqpf</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>650</v>
+      </c>
+      <c r="R47" t="n">
+        <v>813</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1892925915</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1892925915</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>바디마인퍼스널트레이닝 2호점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>bodymine2@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>02-2611-2202</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 12 5층 501호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5v8</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>113</v>
+      </c>
+      <c r="R48" t="n">
+        <v>187</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1891984160</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1891984160</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>머스타드피트니스 철산역점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mustardfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1414-7199</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 20 야우리빌딩 10층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://www.mustard-fitness.com/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43cl1</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1551</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>205</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1756</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>12762047</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12762047</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>070-8914-4524</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하2동</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1741252859</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1741252859</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>써니업 여성맞춤 피트니스 광명하안점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sunnyupfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02-6956-0202</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 9 4층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yvoj</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>177</v>
+      </c>
+      <c r="R51" t="n">
+        <v>313</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1046530777</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046530777</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>스마일휘트니스 헬스&amp;PT 소하점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>smile_fitness_soha@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>02-899-5249</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 351 동림프라자 5층 스마일 휘트니스</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>115</v>
+      </c>
+      <c r="R52" t="n">
+        <v>235</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>12815627</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/12815627</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>휘트니스엠 헬스&amp;pt 하안점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>fitnessm10@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1444-0167</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로288번길 15 조일프라자 5층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43k9f</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1613</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>343</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1956</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>20076918</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20076918</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>프라임짐 헬스 PT 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>primegym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1339-2581</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 986 6층 1호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/primegym4</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdcabj7</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>675</v>
+      </c>
+      <c r="R54" t="n">
+        <v>911</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2032025487</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032025487</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>클리어짐 철산역점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cleargym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1371-1045</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로854번길 16 금강빌딩 4층 401호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcsoke</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1925</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>624</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2549</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1477285733</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1477285733</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>리본필라테스 광명철산점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>reborn_gusnak@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>hello@rebornpilates.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02-2617-2227</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 광명시 디지털로 13 한국빌딩 6F</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>http://www.rebornpilates.com/cheolsan_studio</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4nw79</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>587</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2746</v>
+      </c>
+      <c r="R56" t="n">
+        <v>3333</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>37039232</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37039232</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>070-8055-4013</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하동</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1692881247</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692881247</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>짐샤크 헬스&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gymshark01@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1348-5703</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 289 태홍빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4777f</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1013</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>298</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1311</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1881875836</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1881875836</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>밸런스PT센터</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>balancept_@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1300-6724</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 광명시 소하로109번길 24 3층 302호(소하동) 밸런스PT센터</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w46uhn</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
         <v>88</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q59" t="n">
         <v>368</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R59" t="n">
         <v>456</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
         <is>
           <t>1493639893</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1493639893</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>휘트니스피플 우먼 철산점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>fpeoplew1@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>psi@fitnesspeople.co.kr</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>02-2625-3912</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로856번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://fitnesspeople.co.kr/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgyxanj</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>468</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>485</v>
+      </c>
+      <c r="R60" t="n">
+        <v>953</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1239968125</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1239968125</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>피티아시바,비티아시바파이프,토류판,유로폼,가설자재임대판매</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>zizoiop@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>070-5258-4099</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 광명시 옥길동</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1294945654</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1294945654</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>070-8914-6613</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 광명시 옥길동</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1846363978</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846363978</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>일루고짐&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>illugowoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1393-1430</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 광명시 안현로 51 3층 일루고짐&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ix7r</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>270</v>
+      </c>
+      <c r="R63" t="n">
+        <v>431</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1747199272</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1747199272</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>학원 등 교습시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>피티수학영어학원</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>greenpcs@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1407-6653</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광복로 66-1 1층 104호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>13</v>
+      </c>
+      <c r="R64" t="n">
+        <v>13</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1071133069</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1071133069</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>영어교육</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>더영어PT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>the_english_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1459-4312</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 광명시 일직로 43 C동 11층 1106호 MERI 세미나실</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>4</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1970648161</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970648161</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>광명 위너복싱</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>winnerboxing_@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1320-3557</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 광명시 도덕로 39 5층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>121</v>
+      </c>
+      <c r="R66" t="n">
+        <v>152</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1982987316</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1982987316</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>광명SK테크노파크휘트니스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>skfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02-898-1003</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 60 광명SK테크노파크 Biz tower 3층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>39</v>
+      </c>
+      <c r="R67" t="n">
+        <v>115</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>34984276</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34984276</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>피지스 피지컬트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>phyzis@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1331-1177</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로651번길 5 501호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>29</v>
+      </c>
+      <c r="R68" t="n">
+        <v>29</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1548977040</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1548977040</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>렛츠핏 하안점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>letsfithaan@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1339-0298</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 314 2층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://bmarket.broj.co.kr/groups/373166261</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49d26</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>770</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>899</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1669</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1590511442</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1590511442</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>벨로짐 PT&amp;스트레치 광명소하점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>bellogym_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1339-0161</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 광명시 금하로 458 웅신아트 304호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://bellogym.kr</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>304</v>
+      </c>
+      <c r="R70" t="n">
+        <v>490</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1250323460</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250323460</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>위무브트레이닝</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>we_move_training1350@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 광명시 철산로 20 지하 2층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/web1ock</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>252</v>
+      </c>
+      <c r="R71" t="n">
+        <v>295</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2053267274</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053267274</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>나인투짐 광명점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ninetwogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1353-2426</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 1005 2층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4s26j</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>192</v>
+      </c>
+      <c r="R72" t="n">
+        <v>255</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1485760457</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1485760457</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>짐고잉 헬스&amp;PT 하안점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>gymgoing@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1336-5596</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 광명시 범안로 1056 701호, 703호, 704호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i5ht9</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>818</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>382</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1687174872</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1687174872</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>프라이드 핏</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pride_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 22 4층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>239</v>
+      </c>
+      <c r="R74" t="n">
+        <v>277</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>767500491</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/767500491</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>짐박스피트니스 철산점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1336-6406</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 광명시 오리로 857 지하1층 짐박스피트니스</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://gymboxx.com/onceinayear?gym=49</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>704</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>104</v>
+      </c>
+      <c r="R75" t="n">
+        <v>808</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1933756441</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1933756441</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>바디채움PT&amp;운동센터 하안점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>bodychaeum@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1378-6854</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wlkbwl8</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>167</v>
+      </c>
+      <c r="R76" t="n">
+        <v>230</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1473047975</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1473047975</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>070-8055-3971</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안동</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1352062282</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1352062282</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>원픽짐PT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>onepickgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1328-1446</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>경기도 광명시 시청로 50 롯데캐슬&amp;SK뷰상가 프라자 B동 202호</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ay8p</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>134</v>
+      </c>
+      <c r="R78" t="n">
+        <v>497</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1142090110</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1142090110</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>라잇나우짐</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>rightnowgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>02-898-5382</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 233 4층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://gorightnowgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wsnt</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>39</v>
+      </c>
+      <c r="R79" t="n">
+        <v>108</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1811074473</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1811074473</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>지앤지휘트니스</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ghdavil@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02-897-9599</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>경기도 광명시 하안로 315 한일빌딩</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>225</v>
+      </c>
+      <c r="R80" t="n">
+        <v>238</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>36481493</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36481493</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>퍼스트라인팀</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>tongee115@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1334-7902</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명역로 28 B1층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>3</v>
+      </c>
+      <c r="R81" t="n">
+        <v>3</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1112785214</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1112785214</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>아놀드짐 ARNOLDGYM PT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>youand1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>02-2612-3111</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광명로 943 3층 아놀드GYM</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/youand1234</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>30</v>
+      </c>
+      <c r="R82" t="n">
+        <v>61</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>17884074</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17884074</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>바른PT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>motionck123@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1435-0616</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>경기도 광명시 광덕산로 5 지하1층 101호 바른pt</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/motionck123</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>39</v>
+      </c>
+      <c r="R83" t="n">
+        <v>44</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>37213704</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37213704</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/광명_PT.xlsx
+++ b/naver-place-crawler/results_health/광명_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>인스타짐 광명역점</t>
+          <t>휘트니스엠 헬스&amp;pt 하안점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>instargymgm@naver.com</t>
+          <t>fitnessm10@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-8069</t>
+          <t>0507-1444-0167</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광명시 일직로12번길 22 라까사호텔 3층</t>
+          <t>경기 광명시 하안로288번길 15 조일프라자 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/instargym_gm/</t>
+          <t>http://pf.kakao.com/_AZJAG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/witsh32</t>
+          <t>https://talk.naver.com/ct/w43k9f</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>896</v>
+        <v>1613</v>
       </c>
       <c r="Q2" t="n">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="R2" t="n">
-        <v>1259</v>
+        <v>1956</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1471490398</t>
+          <t>20076918</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471490398</t>
+          <t>https://m.place.naver.com/place/20076918</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,30 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스엔젤스필라테스 광명점</t>
+          <t>인스타짐 광명역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>haelthangels11@naver.com</t>
+          <t>instargymgm@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1436-8069</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 광명시 범안로 1049 성원빌딩 6층 제1호</t>
+          <t>경기도 광명시 일직로12번길 22 라까사호텔 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/haelthangels11</t>
+          <t>https://www.instagram.com/instargym_gm/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wa8uero</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>219</v>
+        <v>896</v>
       </c>
       <c r="Q3" t="n">
-        <v>53</v>
+        <v>363</v>
       </c>
       <c r="R3" t="n">
-        <v>272</v>
+        <v>1259</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1102369380</t>
+          <t>1471490398</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1102369380</t>
+          <t>https://m.place.naver.com/place/1471490398</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1165,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 광명시 신기로 7 골드스타빌딩 7층</t>
+          <t>경기도 광명시 신기로 7 골드스타빌딩 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1190,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48j21</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1442,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>밸런스PT센터</t>
+          <t>바디채움PT&amp;운동센터 하안점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>balancept_@naver.com</t>
+          <t>bodychaeum@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1300-6724</t>
+          <t>0507-1378-6854</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 광명시 소하로109번길 24 3층 302호(소하동) 밸런스PT센터</t>
+          <t>경기 광명시 하안로287번길 9 대하빌딩 6층 바디채움운동센터</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balancept_</t>
+          <t>https://blog.naver.com/bodychaeum</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46uhn</t>
+          <t>https://talk.naver.com/ct/wlkbwl8</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="Q11" t="n">
-        <v>368</v>
+        <v>167</v>
       </c>
       <c r="R11" t="n">
-        <v>456</v>
+        <v>230</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,15 +1514,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1493639893</t>
+          <t>1473047975</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493639893</t>
+          <t>https://m.place.naver.com/place/1473047975</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GYM101 헬스 PT 광명사거리역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gym101@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1330-3078</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기 광명시 광명로 841 B1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym101_gwangmyeong</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxgpr6n</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>410</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>262</v>
+      </c>
+      <c r="R12" t="n">
+        <v>672</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1261214988</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261214988</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
